--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6BA105-7BE2-4F2C-88C2-636F75B778BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1116ED6-D4A1-46A9-B5F3-E98F6E02C182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7550" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7580" uniqueCount="669">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2180,7 +2180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2221,6 +2221,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2570,7 +2583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1531"/>
+  <dimension ref="A1:E1537"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28249,6 +28262,108 @@
         <v>365</v>
       </c>
     </row>
+    <row r="1532" spans="1:5">
+      <c r="A1532" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1532" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1532" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1532" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1532" s="18" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:5">
+      <c r="A1533" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1533" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1533" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1533" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1533" s="18" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:5" ht="15">
+      <c r="A1534" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1534" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1534" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1534" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:5" ht="15">
+      <c r="A1535" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1535" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1535" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1535" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:5" ht="15">
+      <c r="A1536" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1536" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1536" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1536" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:5" ht="15">
+      <c r="A1537" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1537" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1537" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1537" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1116ED6-D4A1-46A9-B5F3-E98F6E02C182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE4D11E-05C6-4261-A0EC-07285F06D5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7580" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7595" uniqueCount="669">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2180,7 +2180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2221,19 +2221,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2583,7 +2570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1537"/>
+  <dimension ref="A1:E1540"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28263,36 +28250,36 @@
       </c>
     </row>
     <row r="1532" spans="1:5">
-      <c r="A1532" s="16" t="s">
+      <c r="A1532" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B1532" s="17" t="s">
+      <c r="B1532" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C1532" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1532" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1532" s="18" t="s">
+      <c r="C1532" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1532" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1532" s="7" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="1533" spans="1:5">
-      <c r="A1533" s="16" t="s">
+      <c r="A1533" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B1533" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1533" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1533" s="17" t="s">
+      <c r="C1533" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1533" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E1533" s="18" t="s">
+      <c r="E1533" s="7" t="s">
         <v>640</v>
       </c>
     </row>
@@ -28300,7 +28287,7 @@
       <c r="A1534" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B1534" s="17" t="s">
+      <c r="B1534" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C1534" t="s">
@@ -28314,10 +28301,10 @@
       </c>
     </row>
     <row r="1535" spans="1:5" ht="15">
-      <c r="A1535" s="19" t="s">
+      <c r="A1535" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B1535" s="17" t="s">
+      <c r="B1535" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C1535" t="s">
@@ -28331,10 +28318,10 @@
       </c>
     </row>
     <row r="1536" spans="1:5" ht="15">
-      <c r="A1536" s="19" t="s">
+      <c r="A1536" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B1536" s="20" t="s">
+      <c r="B1536" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C1536" t="s">
@@ -28348,10 +28335,10 @@
       </c>
     </row>
     <row r="1537" spans="1:5" ht="15">
-      <c r="A1537" s="19" t="s">
+      <c r="A1537" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B1537" s="20" t="s">
+      <c r="B1537" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C1537" t="s">
@@ -28362,6 +28349,57 @@
       </c>
       <c r="E1537" s="2" t="s">
         <v>658</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:5" ht="15">
+      <c r="A1538" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B1538" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1538" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1538" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:5" ht="15">
+      <c r="A1539" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1539" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1539" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1539" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:5" ht="15">
+      <c r="A1540" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1540" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1540" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1540" s="15" t="s">
+        <v>648</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE4D11E-05C6-4261-A0EC-07285F06D5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1647CEE-BE62-40A0-B1AE-39A614FE6168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7595" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7645" uniqueCount="670">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2046,6 +2046,9 @@
   </si>
   <si>
     <t>Warp Artifact</t>
+  </si>
+  <si>
+    <t>City of Traitors</t>
   </si>
 </sst>
 </file>
@@ -2180,7 +2183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2221,6 +2224,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2570,7 +2579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1540"/>
+  <dimension ref="A1:E1550"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28402,6 +28411,176 @@
         <v>648</v>
       </c>
     </row>
+    <row r="1541" spans="1:5" ht="15">
+      <c r="A1541" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B1541" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1541" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1541" s="17" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:5" ht="15">
+      <c r="A1542" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B1542" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1542" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1542" s="17" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:5" ht="15">
+      <c r="A1543" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1543" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1543" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1543" s="7" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:5" ht="15">
+      <c r="A1544" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1544" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1544" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1544" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:5" ht="15">
+      <c r="A1545" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1545" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1545" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1545" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:5" ht="15">
+      <c r="A1546" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B1546" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1546" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1546" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1546" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:5" ht="15">
+      <c r="A1547" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B1547" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1547" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1547" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:5" ht="15">
+      <c r="A1548" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1548" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1548" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1548" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:5" ht="15">
+      <c r="A1549" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1549" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1549" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1549" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:5" ht="15">
+      <c r="A1550" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1550" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1550" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1550" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1647CEE-BE62-40A0-B1AE-39A614FE6168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEB1A25-34B0-489D-97B5-16F83360561F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2183,7 +2183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2224,12 +2224,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -25994,7 +25988,7 @@
         <v>6</v>
       </c>
       <c r="E1398" s="10" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="1399" spans="1:5" ht="15">
@@ -26147,7 +26141,7 @@
         <v>6</v>
       </c>
       <c r="E1407" s="8" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
     </row>
     <row r="1408" spans="1:5" ht="15">
@@ -28415,16 +28409,16 @@
       <c r="A1541" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B1541" s="16" t="s">
+      <c r="B1541" s="2" t="s">
         <v>286</v>
       </c>
       <c r="C1541" t="s">
         <v>29</v>
       </c>
-      <c r="D1541" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1541" s="17" t="s">
+      <c r="D1541" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1541" s="8" t="s">
         <v>369</v>
       </c>
     </row>
@@ -28432,16 +28426,16 @@
       <c r="A1542" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B1542" s="16" t="s">
+      <c r="B1542" s="2" t="s">
         <v>286</v>
       </c>
       <c r="C1542" t="s">
         <v>29</v>
       </c>
-      <c r="D1542" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1542" s="17" t="s">
+      <c r="D1542" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1542" s="8" t="s">
         <v>369</v>
       </c>
     </row>
@@ -28472,7 +28466,7 @@
       <c r="C1544" t="s">
         <v>2</v>
       </c>
-      <c r="D1544" s="17" t="s">
+      <c r="D1544" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E1544" s="8" t="s">
@@ -28489,7 +28483,7 @@
       <c r="C1545" t="s">
         <v>2</v>
       </c>
-      <c r="D1545" s="17" t="s">
+      <c r="D1545" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E1545" s="8" t="s">
@@ -28517,7 +28511,7 @@
       <c r="A1547" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="B1547" s="16" t="s">
+      <c r="B1547" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C1547" t="s">
@@ -28540,7 +28534,7 @@
       <c r="C1548" t="s">
         <v>2</v>
       </c>
-      <c r="D1548" s="17" t="s">
+      <c r="D1548" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E1548" s="2" t="s">
@@ -28557,7 +28551,7 @@
       <c r="C1549" t="s">
         <v>2</v>
       </c>
-      <c r="D1549" s="17" t="s">
+      <c r="D1549" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E1549" s="2" t="s">
@@ -28574,7 +28568,7 @@
       <c r="C1550" t="s">
         <v>2</v>
       </c>
-      <c r="D1550" s="17" t="s">
+      <c r="D1550" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E1550" s="2" t="s">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEB1A25-34B0-489D-97B5-16F83360561F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03363E45-F4DE-4132-9223-2FDCACC12AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7645" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7660" uniqueCount="670">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2573,7 +2573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1550"/>
+  <dimension ref="A1:E1553"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28575,6 +28575,57 @@
         <v>658</v>
       </c>
     </row>
+    <row r="1551" spans="1:5">
+      <c r="A1551" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1551" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1551" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1551" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:5">
+      <c r="A1552" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1552" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1552" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1552" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:5">
+      <c r="A1553" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1553" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1553" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1553" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03363E45-F4DE-4132-9223-2FDCACC12AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090635A8-1DB6-45B9-8C8C-643B43AEEA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7660" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7690" uniqueCount="671">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2049,6 +2049,9 @@
   </si>
   <si>
     <t>City of Traitors</t>
+  </si>
+  <si>
+    <t>Tundra Wolves</t>
   </si>
 </sst>
 </file>
@@ -2573,7 +2576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1553"/>
+  <dimension ref="A1:E1562"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -5455,23 +5458,6 @@
         <v>374</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15">
-      <c r="A180" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C180" t="s">
-        <v>2</v>
-      </c>
-      <c r="D180" t="s">
-        <v>6</v>
-      </c>
-      <c r="E180" t="s">
-        <v>374</v>
-      </c>
-    </row>
     <row r="181" spans="1:5" ht="15">
       <c r="A181" s="1" t="s">
         <v>51</v>
@@ -24138,23 +24124,6 @@
         <v>640</v>
       </c>
     </row>
-    <row r="1290" spans="1:5" ht="15">
-      <c r="A1290" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B1290" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1290" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1290" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1290" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
     <row r="1291" spans="1:5" ht="15">
       <c r="A1291" s="1" t="s">
         <v>188</v>
@@ -28439,23 +28408,6 @@
         <v>369</v>
       </c>
     </row>
-    <row r="1543" spans="1:5" ht="15">
-      <c r="A1543" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B1543" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1543" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1543" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1543" s="7" t="s">
-        <v>640</v>
-      </c>
-    </row>
     <row r="1544" spans="1:5" ht="15">
       <c r="A1544" s="1" t="s">
         <v>91</v>
@@ -28623,6 +28575,159 @@
         <v>6</v>
       </c>
       <c r="E1553" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:5">
+      <c r="A1554" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1554" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1554" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1554" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:5" ht="15">
+      <c r="A1555" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1555" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1555" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1555" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:5" ht="15">
+      <c r="A1556" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1556" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1556" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1556" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:5">
+      <c r="A1557" t="s">
+        <v>670</v>
+      </c>
+      <c r="B1557" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1557" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1557" s="10" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:5">
+      <c r="A1558" t="s">
+        <v>670</v>
+      </c>
+      <c r="B1558" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1558" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1558" s="10" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:5" ht="15">
+      <c r="A1559" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1559" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1559" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1559" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:5" ht="15">
+      <c r="A1560" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1560" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1560" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1560" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:5" ht="15">
+      <c r="A1561" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1561" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1561" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1561" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:5" ht="15">
+      <c r="A1562" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1562" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1562" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1562" s="2" t="s">
         <v>640</v>
       </c>
     </row>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090635A8-1DB6-45B9-8C8C-643B43AEEA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA838C9-0097-4AA5-9D52-361D3BDF4A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-38535" yWindow="-1590" windowWidth="38670" windowHeight="21150" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7690" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="671">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2576,7 +2577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1562"/>
+  <dimension ref="A1:E1564"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28731,6 +28732,40 @@
         <v>640</v>
       </c>
     </row>
+    <row r="1563" spans="1:5" ht="15">
+      <c r="A1563" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1563" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1563" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1563" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:5" ht="15">
+      <c r="A1564" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1564" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1564" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1564" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA838C9-0097-4AA5-9D52-361D3BDF4A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333D1B66-9E9E-4470-B3E0-7265857BFB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38535" yWindow="-1590" windowWidth="38670" windowHeight="21150" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
+    <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7700" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7710" uniqueCount="671">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2187,7 +2186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2228,6 +2227,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2577,7 +2585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1564"/>
+  <dimension ref="A1:E1566"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28766,6 +28774,40 @@
         <v>365</v>
       </c>
     </row>
+    <row r="1565" spans="1:5" ht="15">
+      <c r="A1565" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1565" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1565" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1565" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1565" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:5">
+      <c r="A1566" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1566" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1566" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1566" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1566" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333D1B66-9E9E-4470-B3E0-7265857BFB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CFC2A3-B360-4851-BB17-6700EDD0F38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7710" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7725" uniqueCount="671">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2186,7 +2186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2227,15 +2227,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2585,7 +2576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1566"/>
+  <dimension ref="A1:E1569"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28792,20 +28783,71 @@
       </c>
     </row>
     <row r="1566" spans="1:5">
-      <c r="A1566" s="16" t="s">
+      <c r="A1566" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B1566" s="17" t="s">
+      <c r="B1566" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1566" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1566" s="17" t="s">
+      <c r="C1566" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1566" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E1566" s="18" t="s">
+      <c r="E1566" s="10" t="s">
         <v>365</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:5" ht="15">
+      <c r="A1567" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1567" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1567" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1567" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:5" ht="15">
+      <c r="A1568" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1568" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1568" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1568" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:5" ht="15">
+      <c r="A1569" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1569" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1569" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1569" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CFC2A3-B360-4851-BB17-6700EDD0F38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE07CF46-3200-439D-815D-A3D0014A40F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1575" windowWidth="38640" windowHeight="21120" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7725" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7820" uniqueCount="672">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2052,6 +2052,9 @@
   </si>
   <si>
     <t>Tundra Wolves</t>
+  </si>
+  <si>
+    <t>UR Blue Red</t>
   </si>
 </sst>
 </file>
@@ -2186,7 +2189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2227,6 +2230,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2576,7 +2589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1569"/>
+  <dimension ref="A1:E1597"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -8399,23 +8412,6 @@
         <v>366</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15">
-      <c r="A360" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C360" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D360" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E360" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
     <row r="361" spans="1:5" ht="15">
       <c r="A361" s="1" t="s">
         <v>186</v>
@@ -8535,23 +8531,6 @@
         <v>366</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="15">
-      <c r="A368" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C368" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D368" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E368" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
     <row r="369" spans="1:5" ht="15">
       <c r="A369" s="1" t="s">
         <v>107</v>
@@ -12224,23 +12203,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="585" spans="1:5">
-      <c r="A585" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B585" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C585" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D585" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E585" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="586" spans="1:5">
       <c r="A586" s="2" t="s">
         <v>30</v>
@@ -12258,40 +12220,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="587" spans="1:5">
-      <c r="A587" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B587" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C587" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D587" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E587" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="588" spans="1:5">
-      <c r="A588" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B588" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C588" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D588" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E588" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="589" spans="1:5" ht="15">
       <c r="A589" s="1" t="s">
         <v>376</v>
@@ -20758,40 +20686,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1090" spans="1:5" ht="15">
-      <c r="A1090" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1090" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1090" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1090" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1090" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1091" spans="1:5" ht="15">
-      <c r="A1091" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1091" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1091" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1091" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1091" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1094" spans="1:5" ht="15">
       <c r="A1094" s="1" t="s">
         <v>597</v>
@@ -28011,7 +27905,7 @@
         <v>29</v>
       </c>
       <c r="D1519" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E1519" s="7" t="s">
         <v>365</v>
@@ -28019,7 +27913,7 @@
     </row>
     <row r="1520" spans="1:5" ht="15">
       <c r="A1520" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B1520" s="3" t="s">
         <v>41</v>
@@ -28028,32 +27922,15 @@
         <v>29</v>
       </c>
       <c r="D1520" s="2" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E1520" s="7" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="1521" spans="1:5" ht="15">
-      <c r="A1521" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1521" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1521" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1521" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1521" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1522" spans="1:5" ht="15">
       <c r="A1522" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B1522" s="3" t="s">
         <v>41</v>
@@ -28070,36 +27947,36 @@
     </row>
     <row r="1523" spans="1:5" ht="15">
       <c r="A1523" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1523" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1523" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1523" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1523" s="7" t="s">
-        <v>365</v>
+        <v>184</v>
+      </c>
+      <c r="B1523" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1523" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1523" s="15" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="1524" spans="1:5" ht="15">
       <c r="A1524" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1524" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1524" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1524" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1524" s="7" t="s">
-        <v>365</v>
+        <v>184</v>
+      </c>
+      <c r="B1524" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1524" s="15" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="1525" spans="1:5" ht="15">
@@ -28183,84 +28060,84 @@
       <c r="D1529" t="s">
         <v>6</v>
       </c>
-      <c r="E1529" s="15" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="1530" spans="1:5" ht="15">
-      <c r="A1530" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1530" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1530" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1530" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1530" s="15" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="1531" spans="1:5" ht="15">
-      <c r="A1531" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1531" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1531" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1531" t="s">
-        <v>6</v>
+      <c r="E1529" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:5">
+      <c r="A1530" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1530" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1530" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1530" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1530" s="7" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:5">
+      <c r="A1531" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1531" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1531" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1531" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E1531" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1532" spans="1:5">
-      <c r="A1532" s="5" t="s">
-        <v>49</v>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:5" ht="15">
+      <c r="A1532" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="B1532" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C1532" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1532" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1532" s="7" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="1533" spans="1:5">
-      <c r="A1533" s="5" t="s">
-        <v>49</v>
+      <c r="C1532" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1532" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1532" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:5" ht="15">
+      <c r="A1533" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="B1533" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1533" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1533" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1533" s="7" t="s">
-        <v>640</v>
+        <v>58</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1533" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1533" s="2" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="1534" spans="1:5" ht="15">
       <c r="A1534" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="B1534" s="3" t="s">
-        <v>58</v>
+        <v>169</v>
+      </c>
+      <c r="B1534" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C1534" t="s">
         <v>2</v>
@@ -28274,16 +28151,16 @@
     </row>
     <row r="1535" spans="1:5" ht="15">
       <c r="A1535" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B1535" s="3" t="s">
-        <v>58</v>
+        <v>169</v>
+      </c>
+      <c r="B1535" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C1535" t="s">
         <v>2</v>
       </c>
-      <c r="D1535" t="s">
-        <v>6</v>
+      <c r="D1535" s="6" t="s">
+        <v>3</v>
       </c>
       <c r="E1535" s="2" t="s">
         <v>658</v>
@@ -28291,24 +28168,24 @@
     </row>
     <row r="1536" spans="1:5" ht="15">
       <c r="A1536" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B1536" s="2" t="s">
-        <v>76</v>
+        <v>643</v>
+      </c>
+      <c r="B1536" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C1536" t="s">
         <v>2</v>
       </c>
-      <c r="D1536" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1536" s="2" t="s">
-        <v>658</v>
+      <c r="D1536" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1536" s="15" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="1537" spans="1:5" ht="15">
       <c r="A1537" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B1537" s="2" t="s">
         <v>76</v>
@@ -28317,24 +28194,24 @@
         <v>2</v>
       </c>
       <c r="D1537" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1537" s="2" t="s">
-        <v>658</v>
+        <v>6</v>
+      </c>
+      <c r="E1537" s="15" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="1538" spans="1:5" ht="15">
       <c r="A1538" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="B1538" s="1" t="s">
-        <v>84</v>
+        <v>175</v>
+      </c>
+      <c r="B1538" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C1538" t="s">
         <v>2</v>
       </c>
-      <c r="D1538" t="s">
-        <v>42</v>
+      <c r="D1538" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="E1538" s="15" t="s">
         <v>648</v>
@@ -28342,117 +28219,117 @@
     </row>
     <row r="1539" spans="1:5" ht="15">
       <c r="A1539" s="1" t="s">
-        <v>175</v>
+        <v>669</v>
       </c>
       <c r="B1539" s="2" t="s">
-        <v>76</v>
+        <v>286</v>
       </c>
       <c r="C1539" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1539" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1539" s="15" t="s">
-        <v>648</v>
+        <v>29</v>
+      </c>
+      <c r="D1539" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1539" s="8" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="1540" spans="1:5" ht="15">
       <c r="A1540" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1540" s="3" t="s">
-        <v>58</v>
+        <v>669</v>
+      </c>
+      <c r="B1540" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="C1540" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1540" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1540" s="15" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="1541" spans="1:5" ht="15">
-      <c r="A1541" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="B1541" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C1541" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1541" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1541" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1540" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1540" s="8" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="1542" spans="1:5" ht="15">
       <c r="A1542" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="B1542" s="2" t="s">
-        <v>286</v>
+        <v>91</v>
+      </c>
+      <c r="B1542" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C1542" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D1542" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E1542" s="8" t="s">
-        <v>369</v>
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:5" ht="15">
+      <c r="A1543" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1543" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1543" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1543" s="8" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="1544" spans="1:5" ht="15">
       <c r="A1544" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1544" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1544" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1544" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1544" s="8" t="s">
-        <v>663</v>
+        <v>457</v>
+      </c>
+      <c r="B1544" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1544" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1544" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1544" s="2" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="1545" spans="1:5" ht="15">
       <c r="A1545" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1545" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B1545" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C1545" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1545" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1545" s="8" t="s">
-        <v>663</v>
+        <v>29</v>
+      </c>
+      <c r="D1545" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1545" s="2" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="1546" spans="1:5" ht="15">
       <c r="A1546" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="B1546" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="C1546" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1546" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1546" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1546" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E1546" s="2" t="s">
@@ -28461,15 +28338,15 @@
     </row>
     <row r="1547" spans="1:5" ht="15">
       <c r="A1547" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="B1547" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1547" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C1547" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1547" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1547" s="8" t="s">
         <v>6</v>
       </c>
       <c r="E1547" s="2" t="s">
@@ -28478,7 +28355,7 @@
     </row>
     <row r="1548" spans="1:5" ht="15">
       <c r="A1548" s="1" t="s">
-        <v>91</v>
+        <v>472</v>
       </c>
       <c r="B1548" s="3" t="s">
         <v>58</v>
@@ -28493,38 +28370,38 @@
         <v>658</v>
       </c>
     </row>
-    <row r="1549" spans="1:5" ht="15">
-      <c r="A1549" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1549" s="3" t="s">
-        <v>58</v>
+    <row r="1549" spans="1:5">
+      <c r="A1549" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1549" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C1549" t="s">
         <v>2</v>
       </c>
-      <c r="D1549" s="8" t="s">
+      <c r="D1549" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1549" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="1550" spans="1:5" ht="15">
-      <c r="A1550" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B1550" s="3" t="s">
-        <v>58</v>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:5">
+      <c r="A1550" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1550" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C1550" t="s">
         <v>2</v>
       </c>
-      <c r="D1550" s="8" t="s">
+      <c r="D1550" s="6" t="s">
         <v>6</v>
       </c>
       <c r="E1550" s="2" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1551" spans="1:5">
@@ -28546,121 +28423,104 @@
     </row>
     <row r="1552" spans="1:5">
       <c r="A1552" t="s">
-        <v>645</v>
+        <v>200</v>
       </c>
       <c r="B1552" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1552" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1552" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:5" ht="15">
+      <c r="A1553" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1553" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1552" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1552" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1552" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="1553" spans="1:5">
-      <c r="A1553" t="s">
-        <v>645</v>
-      </c>
-      <c r="B1553" s="2" t="s">
+      <c r="C1553" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1553" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1553" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:5" ht="15">
+      <c r="A1554" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1554" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1553" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1553" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1553" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="1554" spans="1:5">
-      <c r="A1554" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1554" s="2" t="s">
-        <v>642</v>
-      </c>
       <c r="C1554" t="s">
         <v>2</v>
       </c>
-      <c r="D1554" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1554" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="1555" spans="1:5" ht="15">
-      <c r="A1555" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1555" s="1" t="s">
+      <c r="D1554" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1554" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:5">
+      <c r="A1555" t="s">
+        <v>670</v>
+      </c>
+      <c r="B1555" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1555" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1555" s="10" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:5">
+      <c r="A1556" t="s">
+        <v>670</v>
+      </c>
+      <c r="B1556" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1556" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1556" s="10" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:5" ht="15">
+      <c r="A1557" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1557" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1555" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1555" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1555" s="7" t="s">
+      <c r="C1557" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1557" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1557" s="7" t="s">
         <v>365</v>
-      </c>
-    </row>
-    <row r="1556" spans="1:5" ht="15">
-      <c r="A1556" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1556" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1556" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1556" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1556" s="8" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="1557" spans="1:5">
-      <c r="A1557" t="s">
-        <v>670</v>
-      </c>
-      <c r="B1557" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1557" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1557" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1557" s="10" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="1558" spans="1:5">
-      <c r="A1558" t="s">
-        <v>670</v>
-      </c>
-      <c r="B1558" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1558" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1558" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1558" s="10" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="1559" spans="1:5" ht="15">
@@ -28668,160 +28528,160 @@
         <v>472</v>
       </c>
       <c r="B1559" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C1559" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D1559" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1559" s="7" t="s">
-        <v>365</v>
+        <v>6</v>
+      </c>
+      <c r="E1559" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="1560" spans="1:5" ht="15">
       <c r="A1560" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B1560" s="3" t="s">
-        <v>58</v>
+      <c r="B1560" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C1560" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1560" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1560" s="7" t="s">
-        <v>365</v>
+        <v>29</v>
+      </c>
+      <c r="D1560" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1560" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="1561" spans="1:5" ht="15">
       <c r="A1561" s="1" t="s">
-        <v>472</v>
+        <v>52</v>
       </c>
       <c r="B1561" s="1" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C1561" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D1561" t="s">
         <v>6</v>
       </c>
-      <c r="E1561" s="2" t="s">
-        <v>640</v>
+      <c r="E1561" s="7" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="1562" spans="1:5" ht="15">
       <c r="A1562" s="1" t="s">
-        <v>472</v>
+        <v>52</v>
       </c>
       <c r="B1562" s="1" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C1562" t="s">
         <v>29</v>
       </c>
       <c r="D1562" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1562" s="2" t="s">
-        <v>640</v>
+        <v>3</v>
+      </c>
+      <c r="E1562" s="7" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="1563" spans="1:5" ht="15">
       <c r="A1563" s="1" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="B1563" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1563" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1563" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1563" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1564" spans="1:5" ht="15">
-      <c r="A1564" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1564" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1564" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1564" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1564" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1563" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1563" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1563" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:5">
+      <c r="A1564" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1564" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1564" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1564" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1564" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="1565" spans="1:5" ht="15">
       <c r="A1565" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1565" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1565" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1565" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1565" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1565" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1565" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:5" ht="15">
+      <c r="A1566" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1566" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1566" t="s">
         <v>42</v>
       </c>
-      <c r="E1565" s="2" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="1566" spans="1:5">
-      <c r="A1566" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1566" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1566" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1566" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E1566" s="10" t="s">
-        <v>365</v>
+      <c r="E1566" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="1567" spans="1:5" ht="15">
       <c r="A1567" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B1567" s="6" t="s">
-        <v>41</v>
+        <v>103</v>
+      </c>
+      <c r="B1567" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C1567" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D1567" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1567" s="8" t="s">
-        <v>663</v>
+        <v>6</v>
+      </c>
+      <c r="E1567" s="2" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="1568" spans="1:5" ht="15">
       <c r="A1568" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B1568" s="6" t="s">
-        <v>58</v>
+        <v>140</v>
+      </c>
+      <c r="B1568" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C1568" t="s">
         <v>29</v>
@@ -28830,24 +28690,500 @@
         <v>42</v>
       </c>
       <c r="E1568" s="2" t="s">
-        <v>640</v>
+        <v>671</v>
       </c>
     </row>
     <row r="1569" spans="1:5" ht="15">
-      <c r="A1569" s="1" t="s">
+      <c r="A1569" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1569" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1569" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1569" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:5" ht="15">
+      <c r="A1570" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1570" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1570" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1570" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:5" ht="15">
+      <c r="A1571" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1571" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1571" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1571" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:5" ht="15">
+      <c r="A1572" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1572" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1572" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1572" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:5" ht="15">
+      <c r="A1573" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B1569" s="1" t="s">
+      <c r="B1573" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C1569" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1569" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1569" s="2" t="s">
-        <v>640</v>
+      <c r="C1573" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1573" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1573" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:5">
+      <c r="A1574" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1574" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1574" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1574" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1574" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:5">
+      <c r="A1575" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1575" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1575" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1575" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1575" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:5">
+      <c r="A1576" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1576" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1576" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1576" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1576" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:5" ht="15">
+      <c r="A1577" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1577" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1577" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1577" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1577" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:5" ht="15">
+      <c r="A1578" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1578" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1578" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1578" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1578" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:5" ht="15">
+      <c r="A1579" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1579" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1579" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1579" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1579" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:5" ht="15">
+      <c r="A1580" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1580" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1580" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1580" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1580" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:5">
+      <c r="A1581" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1581" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1581" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1581" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1581" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:5">
+      <c r="A1582" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1582" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1582" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1582" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1582" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:5" ht="15">
+      <c r="A1583" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1583" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1583" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1583" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1583" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:5" ht="15">
+      <c r="A1584" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B1584" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1584" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1584" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:5" ht="15">
+      <c r="A1585" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1585" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1585" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1585" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1585" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:5" ht="15">
+      <c r="A1586" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1586" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1586" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1586" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1586" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:5" ht="15">
+      <c r="A1587" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1587" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1587" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1587" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1587" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:5" ht="15">
+      <c r="A1588" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1588" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1588" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1588" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1588" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:5" ht="15">
+      <c r="A1589" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1589" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1589" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1589" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1589" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:5" ht="15">
+      <c r="A1590" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1590" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1590" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1590" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:5" ht="15">
+      <c r="A1591" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B1591" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1591" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1591" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:5" ht="15">
+      <c r="A1592" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1592" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1592" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1592" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1592" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:5" ht="15">
+      <c r="A1593" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1593" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1593" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1593" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1593" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:5" ht="15">
+      <c r="A1594" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1594" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1594" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1594" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:5" ht="15">
+      <c r="A1595" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1595" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1595" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1595" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:5" ht="15">
+      <c r="A1596" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1596" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1596" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1596" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:5" ht="15">
+      <c r="A1597" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1597" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1597" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1597" s="2" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8B85C4-8E0B-4AB1-B74D-B47B78FDAB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932443D1-9BE9-4DA3-995B-BFE075D82359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7805" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7805" uniqueCount="672">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2055,9 +2055,6 @@
   </si>
   <si>
     <t>UR Blue Red</t>
-  </si>
-  <si>
-    <t>N?</t>
   </si>
 </sst>
 </file>
@@ -29121,8 +29118,8 @@
       <c r="C1595" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1595" s="3" t="s">
-        <v>672</v>
+      <c r="D1595" t="s">
+        <v>3</v>
       </c>
       <c r="E1595" s="15" t="s">
         <v>648</v>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30137677-9B7A-4C50-87A2-F6F9BF007BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD09D53-C046-4C21-914A-B7E8A984A307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7915" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7980" uniqueCount="679">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2067,6 +2067,15 @@
   </si>
   <si>
     <t>UG Blue Green</t>
+  </si>
+  <si>
+    <t>UB Blue Black</t>
+  </si>
+  <si>
+    <t>Winter Orb</t>
+  </si>
+  <si>
+    <t>Power Sink</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2244,7 +2253,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2592,7 +2612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1633"/>
+  <dimension ref="A1:E1651"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3686,7 +3706,7 @@
         <v>42</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>365</v>
+        <v>658</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -8177,23 +8197,6 @@
         <v>366</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="15">
-      <c r="A360" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D360" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E360" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
     <row r="361" spans="1:5" ht="15">
       <c r="A361" s="1" t="s">
         <v>188</v>
@@ -13138,7 +13141,7 @@
         <v>39</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="656" spans="1:5" ht="15">
@@ -13631,7 +13634,7 @@
         <v>42</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="685" spans="1:5">
@@ -19479,7 +19482,7 @@
         <v>6</v>
       </c>
       <c r="E1029" s="10" t="s">
-        <v>365</v>
+        <v>676</v>
       </c>
     </row>
     <row r="1030" spans="1:5" ht="15">
@@ -19924,23 +19927,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1060" spans="1:5" ht="15">
-      <c r="A1060" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="B1060" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1060" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1060" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1060" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1061" spans="1:5" ht="15">
       <c r="A1061" s="1" t="s">
         <v>584</v>
@@ -21448,10 +21434,10 @@
         <v>2</v>
       </c>
       <c r="D1153" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1153" s="2" t="s">
-        <v>365</v>
+        <v>676</v>
       </c>
     </row>
     <row r="1154" spans="1:5" ht="15">
@@ -27472,40 +27458,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1510" spans="1:5" ht="15">
-      <c r="A1510" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1510" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1510" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1510" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1510" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1511" spans="1:5" ht="15">
-      <c r="A1511" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B1511" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1511" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1511" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1511" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1512" spans="1:5" ht="15">
       <c r="A1512" s="1" t="s">
         <v>444</v>
@@ -27520,7 +27472,7 @@
         <v>6</v>
       </c>
       <c r="E1512" s="7" t="s">
-        <v>365</v>
+        <v>676</v>
       </c>
     </row>
     <row r="1513" spans="1:5" ht="15">
@@ -27557,23 +27509,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1515" spans="1:5" ht="15">
-      <c r="A1515" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1515" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1515" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1515" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1515" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1517" spans="1:5" ht="15">
       <c r="A1517" s="1" t="s">
         <v>56</v>
@@ -29462,7 +29397,7 @@
       </c>
     </row>
     <row r="1631" spans="1:5" ht="15">
-      <c r="A1631" s="16" t="s">
+      <c r="A1631" s="1" t="s">
         <v>469</v>
       </c>
       <c r="B1631" s="1" t="s">
@@ -29510,6 +29445,312 @@
       </c>
       <c r="E1633" s="15" t="s">
         <v>648</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:5" ht="15">
+      <c r="A1634" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1634" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1634" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1634" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1634" s="10" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:5">
+      <c r="A1635" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1635" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1635" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1635" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1635" s="10" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:5" ht="15">
+      <c r="A1636" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="B1636" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1636" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:5">
+      <c r="A1637" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1637" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1637" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1637" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1637" s="18" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:5" ht="15">
+      <c r="A1638" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1638" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1638" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1638" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1638" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:5" ht="15">
+      <c r="A1639" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1639" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1639" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1639" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1639" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:5" ht="15">
+      <c r="A1640" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1640" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1640" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1640" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1640" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:5" ht="15">
+      <c r="A1641" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1641" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1641" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1641" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1641" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:5" ht="15">
+      <c r="A1642" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1642" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1642" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1642" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1642" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:5" ht="15">
+      <c r="A1643" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1643" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1643" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1643" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1643" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:5" ht="15">
+      <c r="A1644" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1644" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1644" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1644" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1644" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:5" ht="15">
+      <c r="A1645" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1645" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1645" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1645" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1645" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:5" ht="15">
+      <c r="A1646" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B1646" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1646" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1646" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1646" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:5" ht="15">
+      <c r="A1647" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B1647" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1647" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1647" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1647" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:5" ht="15">
+      <c r="A1648" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B1648" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1648" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1648" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:5" ht="15">
+      <c r="A1649" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B1649" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1649" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1649" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:5" ht="15">
+      <c r="A1650" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1650" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1650" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1650" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:5">
+      <c r="A1651" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1651" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1651" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1651" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1651" s="7" t="s">
+        <v>676</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD09D53-C046-4C21-914A-B7E8A984A307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12032AFF-F829-4EE6-9BCF-00D9638EE8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -2210,7 +2210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2251,18 +2251,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -19482,7 +19470,7 @@
         <v>6</v>
       </c>
       <c r="E1029" s="10" t="s">
-        <v>676</v>
+        <v>365</v>
       </c>
     </row>
     <row r="1030" spans="1:5" ht="15">
@@ -26806,10 +26794,10 @@
         <v>2</v>
       </c>
       <c r="D1471" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E1471" s="2" t="s">
-        <v>365</v>
+        <v>676</v>
       </c>
     </row>
     <row r="1472" spans="1:5" ht="15">
@@ -29499,19 +29487,19 @@
       </c>
     </row>
     <row r="1637" spans="1:5">
-      <c r="A1637" s="16" t="s">
+      <c r="A1637" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B1637" s="17" t="s">
+      <c r="B1637" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C1637" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1637" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1637" s="18" t="s">
+      <c r="C1637" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1637" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1637" s="7" t="s">
         <v>366</v>
       </c>
     </row>
@@ -29658,7 +29646,7 @@
       <c r="B1646" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C1646" s="19" t="s">
+      <c r="C1646" s="2" t="s">
         <v>423</v>
       </c>
       <c r="D1646" s="2" t="s">
@@ -29675,7 +29663,7 @@
       <c r="B1647" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C1647" s="19" t="s">
+      <c r="C1647" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D1647" s="2" t="s">

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12032AFF-F829-4EE6-9BCF-00D9638EE8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C430E6-59A8-46BE-AB46-B914F459DDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7980" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8085" uniqueCount="681">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2076,6 +2076,12 @@
   </si>
   <si>
     <t>Power Sink</t>
+  </si>
+  <si>
+    <t>UW Blue White</t>
+  </si>
+  <si>
+    <t>WB White Black</t>
   </si>
 </sst>
 </file>
@@ -2210,7 +2216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2251,6 +2257,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2600,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1651"/>
+  <dimension ref="A1:E1691"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -3357,40 +3372,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
         <v>44</v>
@@ -3408,74 +3389,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2" t="s">
         <v>45</v>
@@ -4156,23 +4069,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2" t="s">
         <v>33</v>
@@ -5788,23 +5684,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="15">
-      <c r="A204" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C204" t="s">
-        <v>2</v>
-      </c>
-      <c r="D204" t="s">
-        <v>42</v>
-      </c>
-      <c r="E204" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2" t="s">
         <v>17</v>
@@ -7182,23 +7061,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="15">
-      <c r="A286" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E286" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="287" spans="1:5" ht="15">
       <c r="A287" s="1" t="s">
         <v>164</v>
@@ -7420,23 +7282,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="15">
-      <c r="A314" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E314" s="10" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="315" spans="1:5" ht="15">
       <c r="A315" s="1" t="s">
         <v>129</v>
@@ -13115,23 +12960,6 @@
         <v>366</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="15">
-      <c r="A655" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B655" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C655" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D655" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E655" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="656" spans="1:5" ht="15">
       <c r="A656" s="1" t="s">
         <v>230</v>
@@ -13608,23 +13436,6 @@
         <v>366</v>
       </c>
     </row>
-    <row r="684" spans="1:5">
-      <c r="A684" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B684" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C684" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D684" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E684" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="685" spans="1:5">
       <c r="A685" s="5" t="s">
         <v>59</v>
@@ -19830,23 +19641,6 @@
         <v>365</v>
       </c>
     </row>
-    <row r="1054" spans="1:5" ht="15">
-      <c r="A1054" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1054" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1054" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1054" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1054" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1055" spans="1:5" ht="15">
       <c r="A1055" s="1" t="s">
         <v>541</v>
@@ -27429,23 +27223,6 @@
         <v>663</v>
       </c>
     </row>
-    <row r="1509" spans="1:5" ht="15">
-      <c r="A1509" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1509" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1509" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1509" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1509" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1512" spans="1:5" ht="15">
       <c r="A1512" s="1" t="s">
         <v>444</v>
@@ -28126,40 +27903,6 @@
         <v>640</v>
       </c>
     </row>
-    <row r="1556" spans="1:5" ht="15">
-      <c r="A1556" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1556" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1556" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1556" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1556" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1557" spans="1:5" ht="15">
-      <c r="A1557" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1557" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1557" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1557" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1557" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1558" spans="1:5" ht="15">
       <c r="A1558" s="1" t="s">
         <v>132</v>
@@ -28840,57 +28583,6 @@
         <v>671</v>
       </c>
     </row>
-    <row r="1599" spans="1:5" ht="15">
-      <c r="A1599" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="B1599" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1599" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1599" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1599" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1600" spans="1:5" ht="15">
-      <c r="A1600" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1600" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1600" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1600" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1600" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="1601" spans="1:5" ht="15">
-      <c r="A1601" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B1601" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1601" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1601" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1601" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
     <row r="1602" spans="1:5" ht="15">
       <c r="A1602" s="1" t="s">
         <v>659</v>
@@ -29739,6 +29431,686 @@
       </c>
       <c r="E1651" s="7" t="s">
         <v>676</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:5">
+      <c r="A1652" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1652" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1652" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1652" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1652" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:5">
+      <c r="A1653" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1653" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1653" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1653" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1653" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:5">
+      <c r="A1654" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1654" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1654" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1654" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1654" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:5">
+      <c r="A1655" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1655" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1655" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1655" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1655" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:5">
+      <c r="A1656" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1656" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1656" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1656" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1656" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:5">
+      <c r="A1657" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1657" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1657" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1657" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1657" s="18" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:5">
+      <c r="A1658" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1658" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1658" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1658" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1658" s="7" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:5" ht="15">
+      <c r="A1659" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1659" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1659" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:5" ht="15">
+      <c r="A1660" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1660" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1660" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1660" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1660" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:5" ht="15">
+      <c r="A1661" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1661" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1661" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:5" ht="15">
+      <c r="A1662" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1662" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1662" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:5" ht="15">
+      <c r="A1663" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B1663" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1663" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:5" ht="15">
+      <c r="A1664" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1664" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1664" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1664" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1664" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:5" ht="15">
+      <c r="A1665" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1665" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1665" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1665" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1665" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:5" ht="15">
+      <c r="A1666" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1666" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1666" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:5">
+      <c r="A1667" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1667" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1667" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1667" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:5">
+      <c r="A1668" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1668" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1668" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1668" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:5">
+      <c r="A1669" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1669" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1669" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1669" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:5">
+      <c r="A1670" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1670" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1670" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1670" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1670" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:5">
+      <c r="A1671" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1671" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1671" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1671" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1671" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:5">
+      <c r="A1672" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1672" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1672" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1672" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:5">
+      <c r="A1673" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1673" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1673" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1673" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:5" ht="15">
+      <c r="A1674" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1674" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1674" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:5" ht="15">
+      <c r="A1675" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1675" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1675" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:5" ht="15">
+      <c r="A1676" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1676" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1676" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:5" ht="15">
+      <c r="A1677" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1677" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1677" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:5">
+      <c r="A1678" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1678" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1678" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1678" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1678" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:5">
+      <c r="A1679" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1679" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1679" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1679" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1679" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:5">
+      <c r="A1680" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1680" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1680" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1680" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1680" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:5" ht="15">
+      <c r="A1681" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1681" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1681" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1681" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1681" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:5" ht="15">
+      <c r="A1682" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B1682" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1682" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:5">
+      <c r="A1683" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1683" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1683" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1683" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1683" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:5">
+      <c r="A1684" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1684" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1684" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1684" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1684" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:5" ht="15">
+      <c r="A1685" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1685" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1685" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1685" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1685" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:5" ht="15">
+      <c r="A1686" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1686" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1686" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1686" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1686" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:5">
+      <c r="A1687" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1687" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1687" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1687" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1687" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:5">
+      <c r="A1688" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1688" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1688" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1688" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1688" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:5">
+      <c r="A1689" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1689" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1689" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1689" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1689" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:5">
+      <c r="A1690" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1690" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1690" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1690" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1690" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:5">
+      <c r="A1691" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1691" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1691" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1691" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1691" s="2" t="s">
+        <v>680</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C430E6-59A8-46BE-AB46-B914F459DDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AF6786-EBEC-4EDC-83B2-6EEB760A50D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8085" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8150" uniqueCount="685">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2082,6 +2082,18 @@
   </si>
   <si>
     <t>WB White Black</t>
+  </si>
+  <si>
+    <t>Soldevi Adnate (V.1)</t>
+  </si>
+  <si>
+    <t>Relic Barrier</t>
+  </si>
+  <si>
+    <t>Red Ward</t>
+  </si>
+  <si>
+    <t>Flight</t>
   </si>
 </sst>
 </file>
@@ -2216,7 +2228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2259,13 +2271,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2615,7 +2621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1691"/>
+  <dimension ref="A1:E1711"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -7486,23 +7492,6 @@
         <v>366</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="15">
-      <c r="A327" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B327" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C327" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D327" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E327" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
     <row r="328" spans="1:5" ht="15">
       <c r="A328" s="1" t="s">
         <v>187</v>
@@ -8030,74 +8019,6 @@
         <v>366</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="15">
-      <c r="A361" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B361" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D361" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E361" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5" ht="15">
-      <c r="A362" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D362" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E362" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5" ht="15">
-      <c r="A363" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B363" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D363" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E363" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5" ht="15">
-      <c r="A364" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B364" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D364" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E364" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
     <row r="365" spans="1:5" ht="15">
       <c r="A365" s="1" t="s">
         <v>193</v>
@@ -21223,21 +21144,9 @@
       </c>
     </row>
     <row r="1154" spans="1:5" ht="15">
-      <c r="A1154" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B1154" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C1154" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1154" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1154" s="2" t="s">
-        <v>369</v>
-      </c>
+      <c r="A1154" s="1"/>
+      <c r="B1154" s="2"/>
+      <c r="E1154" s="2"/>
     </row>
     <row r="1155" spans="1:5" ht="15">
       <c r="A1155" s="1" t="s">
@@ -27394,21 +27303,9 @@
       </c>
     </row>
     <row r="1524" spans="1:5" ht="15">
-      <c r="A1524" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1524" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1524" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1524" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1524" s="7" t="s">
-        <v>365</v>
-      </c>
+      <c r="A1524" s="1"/>
+      <c r="B1524" s="1"/>
+      <c r="E1524" s="7"/>
     </row>
     <row r="1525" spans="1:5">
       <c r="A1525" s="5" t="s">
@@ -27866,8 +27763,13 @@
         <v>42</v>
       </c>
       <c r="E1552" s="7" t="s">
-        <v>365</v>
-      </c>
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:5" ht="15">
+      <c r="A1553" s="1"/>
+      <c r="B1553" s="1"/>
+      <c r="E1553" s="7"/>
     </row>
     <row r="1554" spans="1:5" ht="15">
       <c r="A1554" s="1" t="s">
@@ -29519,19 +29421,19 @@
       </c>
     </row>
     <row r="1657" spans="1:5">
-      <c r="A1657" s="16" t="s">
+      <c r="A1657" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B1657" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C1657" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1657" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1657" s="18" t="s">
+      <c r="C1657" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1657" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1657" s="7" t="s">
         <v>648</v>
       </c>
     </row>
@@ -30111,6 +30013,346 @@
       </c>
       <c r="E1691" s="2" t="s">
         <v>680</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:5" ht="15">
+      <c r="A1692" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1692" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1692" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1692" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1692" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:5">
+      <c r="A1693" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B1693" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1693" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1693" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1693" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:5" ht="15">
+      <c r="A1694" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1694" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1694" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1694" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1694" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:5" ht="15">
+      <c r="A1695" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1695" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1695" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1695" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1695" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:5" ht="15">
+      <c r="A1696" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1696" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1696" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1696" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1696" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:5" ht="15">
+      <c r="A1697" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1697" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1697" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1697" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1697" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:5" ht="15">
+      <c r="A1698" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1698" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1698" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1698" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1698" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:5" ht="15">
+      <c r="A1699" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1699" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1699" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:5" ht="15">
+      <c r="A1700" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1700" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1700" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:5" ht="15">
+      <c r="A1701" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1701" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1701" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:5" ht="15">
+      <c r="A1702" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1702" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1702" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:5" ht="15">
+      <c r="A1703" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1703" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1703" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1703" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:5" ht="15">
+      <c r="A1704" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1704" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1704" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1704" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1704" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:5" ht="15">
+      <c r="A1705" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1705" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C1705" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1705" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1705" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:5" ht="15">
+      <c r="A1706" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1706" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1706" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1706" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:5" ht="15">
+      <c r="A1707" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1707" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1707" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1707" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1707" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:5" ht="15">
+      <c r="A1708" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B1708" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1708" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1708" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1708" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:5" ht="15">
+      <c r="A1709" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B1709" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1709" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1709" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1709" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:5" ht="15">
+      <c r="A1710" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1710" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1710" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1710" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1710" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:5" ht="15">
+      <c r="A1711" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1711" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1711" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1711" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1711" s="2" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AF6786-EBEC-4EDC-83B2-6EEB760A50D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032CEA25-1AFE-452E-9F39-CFCA1D8A8A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8150" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8200" uniqueCount="685">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2228,7 +2228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2269,9 +2269,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2621,7 +2618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1711"/>
+  <dimension ref="A1:E1721"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -30036,7 +30033,7 @@
       <c r="A1693" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="B1693" s="16" t="s">
+      <c r="B1693" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C1693" s="6" t="s">
@@ -30353,6 +30350,176 @@
       </c>
       <c r="E1711" s="2" t="s">
         <v>365</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:5">
+      <c r="A1712" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1712" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1712" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1712" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1712" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:5">
+      <c r="A1713" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1713" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1713" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1713" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1713" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:5">
+      <c r="A1714" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1714" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1714" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1714" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1714" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:5">
+      <c r="A1715" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1715" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1715" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1715" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1715" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:5" ht="15">
+      <c r="A1716" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1716" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1716" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1716" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1716" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:5" ht="15">
+      <c r="A1717" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1717" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1717" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1717" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1717" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:5" ht="15">
+      <c r="A1718" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1718" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1718" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1718" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1718" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:5" ht="15">
+      <c r="A1719" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1719" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1719" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1719" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1719" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:5">
+      <c r="A1720" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1720" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1720" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1720" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1720" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:5">
+      <c r="A1721" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1721" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1721" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1721" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1721" s="2" t="s">
+        <v>675</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032CEA25-1AFE-452E-9F39-CFCA1D8A8A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63FABCA-4B0D-474C-8917-FD25275C213F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8200" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8360" uniqueCount="694">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2094,6 +2094,33 @@
   </si>
   <si>
     <t>Flight</t>
+  </si>
+  <si>
+    <t>Wall of Swords</t>
+  </si>
+  <si>
+    <t>Stone Rain</t>
+  </si>
+  <si>
+    <t>Wall of Fire</t>
+  </si>
+  <si>
+    <t>Keldon Warlord</t>
+  </si>
+  <si>
+    <t>Bog Wraith </t>
+  </si>
+  <si>
+    <t>Desert Twister</t>
+  </si>
+  <si>
+    <t>Wall of Ice</t>
+  </si>
+  <si>
+    <t>Wall of Brambles</t>
+  </si>
+  <si>
+    <t>Throne of Bone</t>
   </si>
 </sst>
 </file>
@@ -2228,7 +2255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2269,6 +2296,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2618,7 +2648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1721"/>
+  <dimension ref="A1:E1753"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -30522,6 +30552,550 @@
         <v>675</v>
       </c>
     </row>
+    <row r="1722" spans="1:5" ht="15">
+      <c r="A1722" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1722" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1722" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1722" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1722" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:5" ht="15">
+      <c r="A1723" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="B1723" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1723" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1723" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1723" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:5" ht="15">
+      <c r="A1724" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1724" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1724" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:5" ht="15">
+      <c r="A1725" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1725" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1725" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:5" ht="15">
+      <c r="A1726" t="s">
+        <v>686</v>
+      </c>
+      <c r="B1726" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1726" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:5" ht="15">
+      <c r="A1727" t="s">
+        <v>687</v>
+      </c>
+      <c r="B1727" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1727" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:5" ht="15">
+      <c r="A1728" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1728" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1728" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:5" ht="15">
+      <c r="A1729" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1729" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1729" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:5" ht="15">
+      <c r="A1730" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1730" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1730" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:5" ht="15">
+      <c r="A1731" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1731" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1731" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:5" ht="15">
+      <c r="A1732" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1732" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1732" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:5" ht="15">
+      <c r="A1733" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B1733" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1733" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:5" ht="15">
+      <c r="A1734" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B1734" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1734" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:5" ht="15">
+      <c r="A1735" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B1735" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1735" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:5" ht="15">
+      <c r="A1736" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B1736" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1736" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:5" ht="15">
+      <c r="A1737" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1737" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1737" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:5" ht="15">
+      <c r="A1738" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1738" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1738" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:5" ht="15">
+      <c r="A1739" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B1739" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1739" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:5" ht="15">
+      <c r="A1740" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1740" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1740" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1740" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:5">
+      <c r="A1741" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1741" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1741" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1741" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1741" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:5" ht="15">
+      <c r="A1742" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1742" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1742" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1742" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1742" s="10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:5" ht="15">
+      <c r="A1743" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1743" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1743" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1743" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1743" s="10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:5" ht="15">
+      <c r="A1744" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1744" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1744" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1744" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1744" s="10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:5" ht="15">
+      <c r="A1745" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1745" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1745" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1745" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1745" s="10" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:5" ht="15">
+      <c r="A1746" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1746" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1746" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1746" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1746" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:5" ht="15">
+      <c r="A1747" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1747" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1747" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1747" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1747" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:5" ht="15">
+      <c r="A1748" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1748" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1748" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1748" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1748" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:5" ht="15">
+      <c r="A1749" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1749" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1749" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1749" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1749" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:5" ht="15">
+      <c r="A1750" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1750" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1750" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1750" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1750" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:5" ht="15">
+      <c r="A1751" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1751" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1751" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1751" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1751" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:5" ht="15">
+      <c r="A1752" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1752" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1752" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1752" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1752" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:5" ht="15">
+      <c r="A1753" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1753" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1753" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1753" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1753" s="16" t="s">
+        <v>676</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}"/>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63FABCA-4B0D-474C-8917-FD25275C213F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063A00DA-4FC5-4B62-8734-CB0447116231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8360" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8375" uniqueCount="695">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2121,6 +2121,9 @@
   </si>
   <si>
     <t>Throne of Bone</t>
+  </si>
+  <si>
+    <t>Greed</t>
   </si>
 </sst>
 </file>
@@ -2255,7 +2258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2296,9 +2299,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2648,7 +2648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1753"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -30973,7 +30973,7 @@
       <c r="D1746" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1746" s="16" t="s">
+      <c r="E1746" s="8" t="s">
         <v>676</v>
       </c>
     </row>
@@ -30990,7 +30990,7 @@
       <c r="D1747" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1747" s="16" t="s">
+      <c r="E1747" s="8" t="s">
         <v>676</v>
       </c>
     </row>
@@ -31007,7 +31007,7 @@
       <c r="D1748" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1748" s="16" t="s">
+      <c r="E1748" s="8" t="s">
         <v>676</v>
       </c>
     </row>
@@ -31024,7 +31024,7 @@
       <c r="D1749" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1749" s="16" t="s">
+      <c r="E1749" s="8" t="s">
         <v>676</v>
       </c>
     </row>
@@ -31041,7 +31041,7 @@
       <c r="D1750" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1750" s="16" t="s">
+      <c r="E1750" s="8" t="s">
         <v>676</v>
       </c>
     </row>
@@ -31058,7 +31058,7 @@
       <c r="D1751" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1751" s="16" t="s">
+      <c r="E1751" s="8" t="s">
         <v>676</v>
       </c>
     </row>
@@ -31075,7 +31075,7 @@
       <c r="D1752" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1752" s="16" t="s">
+      <c r="E1752" s="8" t="s">
         <v>676</v>
       </c>
     </row>
@@ -31092,8 +31092,59 @@
       <c r="D1753" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1753" s="16" t="s">
+      <c r="E1753" s="8" t="s">
         <v>676</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:5" ht="15">
+      <c r="A1754" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1754" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1754" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1754" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:5" ht="15">
+      <c r="A1755" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B1755" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1755" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1755" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1755" s="8" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:5" ht="15">
+      <c r="A1756" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1756" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1756" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1756" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1756" s="2" t="s">
+        <v>648</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063A00DA-4FC5-4B62-8734-CB0447116231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36344522-2ECD-4A3E-AABF-73433D81910A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8375" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8725" uniqueCount="706">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2124,6 +2125,39 @@
   </si>
   <si>
     <t>Greed</t>
+  </si>
+  <si>
+    <t>Stasis</t>
+  </si>
+  <si>
+    <t>Underground Sea</t>
+  </si>
+  <si>
+    <t>Phantom Monster</t>
+  </si>
+  <si>
+    <t>Orcish Oriflamme</t>
+  </si>
+  <si>
+    <t>Smoke</t>
+  </si>
+  <si>
+    <t>Roc of Kher Ridges</t>
+  </si>
+  <si>
+    <t>Earthbind </t>
+  </si>
+  <si>
+    <t>Wooden Sphere</t>
+  </si>
+  <si>
+    <t>Veteran Bodyguard</t>
+  </si>
+  <si>
+    <t>Rocket Launcher</t>
+  </si>
+  <si>
+    <t>Mountain (V.1) </t>
   </si>
 </sst>
 </file>
@@ -2258,7 +2292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2301,6 +2335,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2648,7 +2692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1830"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -28206,74 +28250,6 @@
         <v>671</v>
       </c>
     </row>
-    <row r="1581" spans="1:5" ht="15">
-      <c r="A1581" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="B1581" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1581" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1581" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1581" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="1582" spans="1:5" ht="15">
-      <c r="A1582" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B1582" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1582" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1582" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1582" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="1583" spans="1:5" ht="15">
-      <c r="A1583" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B1583" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1583" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1583" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1583" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="1584" spans="1:5" ht="15">
-      <c r="A1584" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="B1584" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1584" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1584" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1584" s="2" t="s">
-        <v>671</v>
-      </c>
-    </row>
     <row r="1585" spans="1:5" ht="15">
       <c r="A1585" s="1" t="s">
         <v>472</v>
@@ -29944,11 +29920,11 @@
       <c r="A1686" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B1686" s="1" t="s">
-        <v>76</v>
+      <c r="B1686" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C1686" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D1686" s="2" t="s">
         <v>6</v>
@@ -31145,6 +31121,1264 @@
       </c>
       <c r="E1756" s="2" t="s">
         <v>648</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:5" ht="15">
+      <c r="A1757" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="B1757" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1757" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1757" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1757" s="8" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:5" ht="15">
+      <c r="A1758" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B1758" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1758" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1758" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1758" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:5" ht="15">
+      <c r="A1759" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B1759" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1759" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1759" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1759" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:5" ht="15">
+      <c r="A1760" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1760" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1760" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1760" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1760" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:5" ht="15">
+      <c r="A1761" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B1761" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1761" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1761" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1761" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:5" ht="15">
+      <c r="A1762" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1762" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1762" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1762" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1762" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:5" ht="15">
+      <c r="A1763" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B1763" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1763" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1763" s="8" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:5" ht="15">
+      <c r="A1764" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1764" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1764" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1764" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:5" ht="15">
+      <c r="A1765" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B1765" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1765" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1765" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:5" ht="15">
+      <c r="A1766" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B1766" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1766" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:5" ht="15">
+      <c r="A1767" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B1767" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1767" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:5" ht="15">
+      <c r="A1768" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B1768" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1768" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1768" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:5" ht="15">
+      <c r="A1769" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B1769" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1769" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:5" ht="15">
+      <c r="A1770" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B1770" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1770" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1770" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:5" ht="15">
+      <c r="A1771" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1771" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1771" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1771" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1771" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:5" ht="15">
+      <c r="A1772" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1772" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1772" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1772" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1772" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:5" ht="15">
+      <c r="A1773" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1773" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1773" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1773" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1773" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:5" ht="15">
+      <c r="A1774" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1774" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1774" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1774" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1774" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:5" ht="15">
+      <c r="A1775" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1775" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1775" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1775" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1775" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:5" ht="15">
+      <c r="A1776" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1776" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1776" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1776" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1776" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:5" ht="15">
+      <c r="A1777" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1777" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1777" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1777" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1777" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:5" ht="15">
+      <c r="A1778" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B1778" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1778" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1778" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:5" ht="15">
+      <c r="A1779" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1779" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1779" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:5" ht="15">
+      <c r="A1780" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1780" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1780" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1780" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1780" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:5" ht="15">
+      <c r="A1781" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1781" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1781" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1781" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1781" s="15" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:5" ht="15">
+      <c r="A1782" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="B1782" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1782" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1782" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1782" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:5">
+      <c r="A1783" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1783" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1783" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1783" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1783" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:5" ht="15">
+      <c r="A1784" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1784" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1784" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1784" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1784" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:5" ht="15">
+      <c r="A1785" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1785" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1785" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1785" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1785" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:5" ht="15">
+      <c r="A1786" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1786" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1786" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1786" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1786" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:5" ht="15">
+      <c r="A1787" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1787" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1787" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1787" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1787" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:5" ht="15">
+      <c r="A1788" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1788" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1788" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1788" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1788" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:5" ht="15">
+      <c r="A1789" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1789" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1789" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1789" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1789" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:5" ht="15">
+      <c r="A1790" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1790" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1790" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1790" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1790" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:5">
+      <c r="A1791" t="s">
+        <v>651</v>
+      </c>
+      <c r="B1791" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1791" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1791" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1791" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:5" ht="15">
+      <c r="A1792" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1792" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1792" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1792" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1792" s="8" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:5" ht="15">
+      <c r="A1793" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1793" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1793" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1793" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1793" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:5" ht="15">
+      <c r="A1794" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1794" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1794" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1794" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1794" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:5" ht="15">
+      <c r="A1795" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1795" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1795" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1795" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1795" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:5" ht="15">
+      <c r="A1796" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1796" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1796" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1796" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1796" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:5" ht="15">
+      <c r="A1797" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1797" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1797" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1797" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1797" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:5" ht="15">
+      <c r="A1798" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1798" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1798" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1798" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1798" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:5" ht="15">
+      <c r="A1799" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1799" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1799" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1799" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1799" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:5" ht="15">
+      <c r="A1800" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1800" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1800" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1800" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1800" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:5" ht="15">
+      <c r="A1801" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1801" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1801" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1801" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1801" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:5" ht="15">
+      <c r="A1802" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1802" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1802" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1802" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1802" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:5" ht="15">
+      <c r="A1803" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1803" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1803" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1803" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1803" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:5" ht="15">
+      <c r="A1804" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1804" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1804" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1804" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1804" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:5" ht="15">
+      <c r="A1805" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1805" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1805" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1805" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1805" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:5" ht="15">
+      <c r="A1806" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1806" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1806" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1806" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1806" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:5" ht="15">
+      <c r="A1807" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1807" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1807" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1807" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1807" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:5" ht="15">
+      <c r="A1808" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1808" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1808" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1808" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1808" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:5" ht="15">
+      <c r="A1809" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1809" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1809" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1809" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1809" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:5" ht="15">
+      <c r="A1810" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1810" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1810" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1810" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1810" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:5" ht="15">
+      <c r="A1811" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1811" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1811" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1811" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1811" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:5" ht="15">
+      <c r="A1812" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1812" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1812" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1812" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1812" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:5" ht="15">
+      <c r="A1813" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1813" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1813" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1813" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1813" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:5" ht="15">
+      <c r="A1814" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1814" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1814" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1814" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1814" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:5" ht="15">
+      <c r="A1815" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1815" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1815" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1815" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1815" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:5" ht="15">
+      <c r="A1816" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1816" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1816" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1816" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1816" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:5" ht="15">
+      <c r="A1817" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1817" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1817" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1817" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1817" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:5" ht="15">
+      <c r="A1818" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1818" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1818" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1818" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1818" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:5" ht="15">
+      <c r="A1819" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1819" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1819" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1819" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1819" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:5" ht="15">
+      <c r="A1820" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1820" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1820" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1820" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1820" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:5" ht="15">
+      <c r="A1821" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1821" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1821" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1821" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1821" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:5" ht="15">
+      <c r="A1822" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1822" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1822" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1822" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1822" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:5" ht="15">
+      <c r="A1823" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1823" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1823" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1823" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1823" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:5" ht="15">
+      <c r="A1824" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1824" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1824" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1824" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1824" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:5" ht="15">
+      <c r="A1825" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1825" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1825" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1825" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1825" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:5" ht="15">
+      <c r="A1826" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B1826" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1826" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1826" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1826" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:5" ht="15">
+      <c r="A1827" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1827" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1827" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1827" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1827" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:5" ht="15">
+      <c r="A1828" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1828" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1828" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1828" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1828" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:5" ht="15">
+      <c r="A1829" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1829" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1829" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1829" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1829" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:5" ht="15">
+      <c r="A1830" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B1830" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1830" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1830" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1830" s="2" t="s">
+        <v>680</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/collection.xlsx
+++ b/uploads/collection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sokom\Documents\mtg-portfolio2\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36344522-2ECD-4A3E-AABF-73433D81910A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D194D65D-9DE7-409C-8933-86CB7695C4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0FB49C1A-78A4-4DA0-A11D-346B115E728B}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8725" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8765" uniqueCount="707">
   <si>
     <t>Llanowar Elves</t>
   </si>
@@ -2158,6 +2157,9 @@
   </si>
   <si>
     <t>Mountain (V.1) </t>
+  </si>
+  <si>
+    <t>Blood Lust</t>
   </si>
 </sst>
 </file>
@@ -2292,7 +2294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2335,16 +2337,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2692,7 +2687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6AFAC-F407-46DB-91C7-9730E2D3F96A}">
-  <dimension ref="A1:E1830"/>
+  <dimension ref="A1:E1838"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
@@ -13518,13 +13513,13 @@
         <v>162</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C690" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D690" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E690" s="2" t="s">
         <v>371</v>
@@ -13535,13 +13530,13 @@
         <v>162</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C691" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D691" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E691" s="2" t="s">
         <v>371</v>
@@ -17270,29 +17265,29 @@
         <v>371</v>
       </c>
     </row>
-    <row r="912" spans="1:5">
+    <row r="912" spans="1:5" ht="15">
       <c r="A912" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B912" s="6" t="s">
-        <v>41</v>
+      <c r="B912" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C912" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D912" s="6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E912" s="2" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="913" spans="1:5">
+    <row r="913" spans="1:5" ht="15">
       <c r="A913" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B913" s="6" t="s">
-        <v>41</v>
+      <c r="B913" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C913" s="6" t="s">
         <v>29</v>
@@ -31515,19 +31510,19 @@
       </c>
     </row>
     <row r="1780" spans="1:5" ht="15">
-      <c r="A1780" s="16" t="s">
+      <c r="A1780" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B1780" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1780" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1780" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1780" s="18" t="s">
+      <c r="C1780" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1780" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1780" s="7" t="s">
         <v>365</v>
       </c>
     </row>
@@ -31549,7 +31544,7 @@
       </c>
     </row>
     <row r="1782" spans="1:5" ht="15">
-      <c r="A1782" s="19" t="s">
+      <c r="A1782" s="1" t="s">
         <v>536</v>
       </c>
       <c r="B1782" s="1" t="s">
@@ -31561,7 +31556,7 @@
       <c r="D1782" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E1782" s="18" t="s">
+      <c r="E1782" s="7" t="s">
         <v>365</v>
       </c>
     </row>
@@ -31600,7 +31595,7 @@
       </c>
     </row>
     <row r="1785" spans="1:5" ht="15">
-      <c r="A1785" s="19" t="s">
+      <c r="A1785" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1785" s="2" t="s">
@@ -31617,7 +31612,7 @@
       </c>
     </row>
     <row r="1786" spans="1:5" ht="15">
-      <c r="A1786" s="19" t="s">
+      <c r="A1786" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B1786" s="2" t="s">
@@ -31634,7 +31629,7 @@
       </c>
     </row>
     <row r="1787" spans="1:5" ht="15">
-      <c r="A1787" s="19" t="s">
+      <c r="A1787" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B1787" s="2" t="s">
@@ -31651,7 +31646,7 @@
       </c>
     </row>
     <row r="1788" spans="1:5" ht="15">
-      <c r="A1788" s="19" t="s">
+      <c r="A1788" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B1788" s="2" t="s">
@@ -31668,7 +31663,7 @@
       </c>
     </row>
     <row r="1789" spans="1:5" ht="15">
-      <c r="A1789" s="19" t="s">
+      <c r="A1789" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B1789" s="2" t="s">
@@ -32378,6 +32373,142 @@
         <v>3</v>
       </c>
       <c r="E1830" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:5" ht="15">
+      <c r="A1831" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B1831" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1831" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1831" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1831" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:5" ht="15">
+      <c r="A1832" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1832" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1832" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1832" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1832" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:5" ht="15">
+      <c r="A1833" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1833" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1833" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1833" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1833" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:5" ht="15">
+      <c r="A1834" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1834" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1834" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1834" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1834" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:5" ht="15">
+      <c r="A1835" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1835" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1835" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1835" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1835" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:5" ht="15">
+      <c r="A1836" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B1836" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1836" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1836" t="s">
+        <v>192</v>
+      </c>
+      <c r="E1836" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:5" ht="15">
+      <c r="A1837" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1837" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1837" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1837" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1837" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:5" ht="15">
+      <c r="A1838" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1838" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1838" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1838" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1838" s="2" t="s">
         <v>680</v>
       </c>
     </row>
